--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486437_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486437_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.174099999999999</v>
+        <v>6.8142</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3463</v>
+        <v>5.7262</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8278</v>
+        <v>1.088</v>
       </c>
       <c r="G2" t="n">
         <v>5.4801</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9593</v>
+        <v>1.5994</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4252</v>
+        <v>0.8051</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5341</v>
+        <v>0.7943</v>
       </c>
       <c r="V2" t="n">
         <v>4.5199</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6719</v>
+        <v>1.6171</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2074</v>
+        <v>0.2759</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4645</v>
+        <v>1.3412</v>
       </c>
       <c r="G3" t="n">
         <v>1.1637</v>
@@ -688,13 +688,13 @@
         <v>0.435</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0308</v>
+        <v>-0.024</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9589</v>
+        <v>-0.8904</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9897</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>1.13</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>R. JOHNSON JR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.5268</v>
+        <v>-0.9399</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8598</v>
+        <v>0.7077</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.667</v>
+        <v>-1.6476</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.2</v>
+        <v>-2.2543</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2677</v>
+        <v>-0.7506</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9323</v>
+        <v>-1.5037</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.3719</v>
+        <v>-1.3393</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4134</v>
+        <v>-0.2333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0415</v>
+        <v>-1.106</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8280999999999999</v>
+        <v>-0.915</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1457</v>
+        <v>-0.5173</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9738</v>
+        <v>-0.3977</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0207</v>
+        <v>0.1845</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8172</v>
+        <v>-0.2331</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2036</v>
+        <v>0.4176</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.13</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.5851</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.9994</v>
+        <v>-1.4163</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8018</v>
+        <v>-0.3728</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1977</v>
+        <v>-1.0436</v>
       </c>
       <c r="G5" t="n">
         <v>0.8673999999999999</v>
@@ -844,13 +844,13 @@
         <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0907</v>
+        <v>0.6738</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2091</v>
+        <v>0.6381</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1184</v>
+        <v>0.0357</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5649999999999999</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. JOHNSON JR</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3044</v>
+        <v>-1.5333</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3486</v>
+        <v>-0.9896</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9558</v>
+        <v>-0.5437</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.2543</v>
+        <v>-1.2</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7506</v>
+        <v>-0.2677</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5037</v>
+        <v>-0.9323</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3393</v>
+        <v>-0.3719</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2333</v>
+        <v>-0.4134</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.106</v>
+        <v>0.0415</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.915</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5173</v>
+        <v>0.1457</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3977</v>
+        <v>-0.9738</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.305</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1801</v>
+        <v>1.0142</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2894</v>
+        <v>0.6874</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1093</v>
+        <v>0.3268</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>-1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>3.5851</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4552</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4903</v>
+        <v>-1.8879</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7617</v>
+        <v>-0.2209</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7287</v>
+        <v>-1.667</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6875</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3254</v>
+        <v>0.277</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.822</v>
+        <v>-0.2812</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4965</v>
+        <v>0.5582</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5649999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1201</v>
+        <v>-2.7857</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8889</v>
+        <v>-1.7086</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2312</v>
+        <v>-1.0771</v>
       </c>
       <c r="G8" t="n">
         <v>0.3439</v>
@@ -1078,13 +1078,13 @@
         <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3563</v>
+        <v>-0.0219</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9589</v>
+        <v>-0.7786999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6026</v>
+        <v>0.7568</v>
       </c>
       <c r="V8" t="n">
         <v>-2.4552</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3399</v>
+        <v>-3.4941</v>
       </c>
       <c r="E9" t="n">
         <v>-3.1696</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1703</v>
+        <v>-0.3245</v>
       </c>
       <c r="G9" t="n">
         <v>-2.0179</v>
@@ -1156,13 +1156,13 @@
         <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0907</v>
+        <v>-0.0634</v>
       </c>
       <c r="T9" t="n">
         <v>-0.6850000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.6216</v>
       </c>
       <c r="V9" t="n">
         <v>-0.7602</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.2131</v>
+        <v>-5.1524</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0128</v>
+        <v>-4.1678</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2003</v>
+        <v>-0.9846</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4799</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0068</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0036</v>
+        <v>-0.1514</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0032</v>
+        <v>0.219</v>
       </c>
       <c r="V10" t="n">
         <v>-1.13</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.148</v>
+        <v>-8.7783</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.289500000000001</v>
+        <v>-3.919499999999998</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.858700000000001</v>
+        <v>-4.858900000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.7845</v>
+        <v>-1.784500000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8971</v>
+        <v>4.897100000000001</v>
       </c>
       <c r="I11" t="n">
         <v>-6.6816</v>
@@ -1312,16 +1312,16 @@
         <v>7.6125</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3372</v>
+        <v>3.7072</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2591</v>
+        <v>-0.8892</v>
       </c>
       <c r="U11" t="n">
-        <v>4.596299999999999</v>
+        <v>4.5964</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1745000000000001</v>
+        <v>0.174500000000001</v>
       </c>
       <c r="W11" t="n">
         <v>11.3204</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.4945</v>
+        <v>7.0404</v>
       </c>
       <c r="E12" t="n">
-        <v>2.096</v>
+        <v>2.4313</v>
       </c>
       <c r="F12" t="n">
-        <v>4.3985</v>
+        <v>4.6091</v>
       </c>
       <c r="G12" t="n">
         <v>2.8111</v>
@@ -1390,13 +1390,13 @@
         <v>3.6976</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5994</v>
+        <v>-0.0535</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6813</v>
+        <v>-0.3461</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0819</v>
+        <v>0.2926</v>
       </c>
       <c r="V12" t="n">
         <v>1.8902</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1812</v>
+        <v>3.3238</v>
       </c>
       <c r="E13" t="n">
-        <v>4.0558</v>
+        <v>4.1676</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8746</v>
+        <v>-0.8438</v>
       </c>
       <c r="G13" t="n">
         <v>2.6325</v>
@@ -1468,13 +1468,13 @@
         <v>2.3926</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1489</v>
+        <v>-0.0063</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5444</v>
+        <v>-0.4326</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3955</v>
+        <v>0.4263</v>
       </c>
       <c r="V13" t="n">
         <v>-1.695</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. GONZALEZ LONGARELA</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.138</v>
+        <v>3.2716</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0634</v>
+        <v>2.7359</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0746</v>
+        <v>0.5357</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1654</v>
+        <v>1.2266</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9064</v>
+        <v>-1.4142</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7411</v>
+        <v>2.6408</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.6401</v>
+        <v>1.6809</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1246</v>
+        <v>-1.3624</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5155999999999999</v>
+        <v>3.0432</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4748</v>
+        <v>-0.4543</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7819</v>
+        <v>-0.0519</v>
       </c>
       <c r="O14" t="n">
-        <v>1.2566</v>
+        <v>-0.4024</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1751</v>
+        <v>1.0875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3926</v>
+        <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0017</v>
+        <v>-0.3677</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3389</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3372</v>
+        <v>0.4675</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>1.3252</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2599</v>
+        <v>1.8902</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.13</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>P. GONZALEZ LONGARELA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0365</v>
+        <v>3.1637</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6241</v>
+        <v>1.0634</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4124</v>
+        <v>2.1003</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2266</v>
+        <v>-0.1654</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4142</v>
+        <v>-0.9064</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6408</v>
+        <v>0.7411</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6809</v>
+        <v>-0.6401</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3624</v>
+        <v>-0.1246</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0432</v>
+        <v>-0.5155999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4543</v>
+        <v>0.4748</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0519</v>
+        <v>-0.7819</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4024</v>
+        <v>1.2566</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6028</v>
+        <v>0.024</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9469</v>
+        <v>-0.3389</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3442</v>
+        <v>0.3629</v>
       </c>
       <c r="V15" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8902</v>
+        <v>2.2599</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1394</v>
+        <v>1.7296</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5866</v>
+        <v>2.0278</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4472</v>
+        <v>-0.2982</v>
       </c>
       <c r="G16" t="n">
         <v>0.298</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2536</v>
+        <v>-0.1562</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3257</v>
+        <v>-0.2331</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0721</v>
+        <v>0.0769</v>
       </c>
       <c r="V16" t="n">
         <v>-0.3698</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4971</v>
+        <v>0.6397</v>
       </c>
       <c r="E17" t="n">
-        <v>0.475</v>
+        <v>0.5868</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0221</v>
+        <v>0.0529</v>
       </c>
       <c r="G17" t="n">
         <v>0.545</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0479</v>
+        <v>0.0946</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U17" t="n">
-        <v>0.089</v>
+        <v>0.1199</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SHELIST</t>
+          <t>M. TOWNES VILLAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8363</v>
+        <v>-1.6082</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6716</v>
+        <v>-3.4478</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5079</v>
+        <v>1.8396</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3785</v>
+        <v>-3.4631</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1618</v>
+        <v>-4.3429</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7833</v>
+        <v>0.8797</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5172</v>
+        <v>-2.674</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2806</v>
+        <v>-3.2111</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7634</v>
+        <v>0.5371</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1388</v>
+        <v>-0.7891</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1188</v>
+        <v>-1.1318</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0199</v>
+        <v>0.3426</v>
       </c>
       <c r="P18" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5225</v>
+        <v>2.8276</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6749000000000001</v>
+        <v>-0.84</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6117</v>
+        <v>-0.8364</v>
       </c>
       <c r="U18" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.0036</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.1947</v>
+        <v>2.2599</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7602</v>
+        <v>2.4552</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.9549</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0701</v>
+        <v>-1.7136</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4095</v>
+        <v>-1.7448</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3394</v>
+        <v>0.0312</v>
       </c>
       <c r="G19" t="n">
         <v>-2.0499</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0875</v>
+        <v>0.444</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1454</v>
+        <v>-0.4807</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2329</v>
+        <v>0.9247</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7602</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. TOWNES VILLAR</t>
+          <t>D. SHELIST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6743</v>
+        <v>-1.7419</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.1183</v>
+        <v>0.8893</v>
       </c>
       <c r="F20" t="n">
-        <v>1.444</v>
+        <v>-2.6312</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4631</v>
+        <v>0.3785</v>
       </c>
       <c r="H20" t="n">
-        <v>-4.3429</v>
+        <v>1.1618</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8797</v>
+        <v>-0.7833</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.674</v>
+        <v>0.5172</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.2111</v>
+        <v>1.2806</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5371</v>
+        <v>-0.7634</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7891</v>
+        <v>-0.1388</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1318</v>
+        <v>-0.1188</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3426</v>
+        <v>-0.0199</v>
       </c>
       <c r="P20" t="n">
-        <v>0.435</v>
+        <v>1.305</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8276</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9061</v>
+        <v>-0.2307</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5069</v>
+        <v>-0.1706</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3992</v>
+        <v>-0.0601</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2599</v>
+        <v>-3.1947</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4552</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>-3.9549</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7578</v>
+        <v>-3.2119</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.186</v>
+        <v>-3.8507</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4282</v>
+        <v>0.6389</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4286</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0464</v>
+        <v>-0.5004999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2329</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1865</v>
+        <v>0.3972</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7602</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>10.1482</v>
+        <v>10.8932</v>
       </c>
       <c r="E22" t="n">
-        <v>4.858700000000001</v>
+        <v>4.8588</v>
       </c>
       <c r="F22" t="n">
-        <v>5.2895</v>
+        <v>6.034499999999998</v>
       </c>
       <c r="G22" t="n">
         <v>1.7847</v>
@@ -2170,13 +2170,13 @@
         <v>18.4881</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.3372</v>
+        <v>-1.5923</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.596299999999999</v>
+        <v>-4.5965</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2591</v>
+        <v>3.004300000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1746000000000005</v>
